--- a/0148_Cuenca_Ushusuma/_raw_reportes_xlsx/IDConfig_64919_completo.xlsx
+++ b/0148_Cuenca_Ushusuma/_raw_reportes_xlsx/IDConfig_64919_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rcf991c7e08e14376"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf13b02ed8cf04770"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,81 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>19/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9041</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9723</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9357</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9724</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9783</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>14/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +339,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.8225</x:v>
+        <x:v>      0.9158</x:v>
       </x:c>
     </x:row>
     <x:row>

--- a/0148_Cuenca_Ushusuma/_raw_reportes_xlsx/IDConfig_64919_completo.xlsx
+++ b/0148_Cuenca_Ushusuma/_raw_reportes_xlsx/IDConfig_64919_completo.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="Rf13b02ed8cf04770"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reporte" sheetId="2" r:id="R68e9db4422154332"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -255,6 +255,756 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>09/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9457</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0529</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0856</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0637</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0743</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0476</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0534</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/10/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0541</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.1901</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2562</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2561</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2449</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.2618</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0736</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9266</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9109</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9315</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9316</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>19/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9216</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>18/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0307</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>17/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8024</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>16/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9164</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>15/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9426</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>14/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0358</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>13/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0412</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>12/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9991</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>11/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8079</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>10/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7978</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>09/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0519</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>08/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9893</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>07/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9632</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>06/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9211</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>05/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9208</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>04/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9001</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>03/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      1.0039</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>02/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7595</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>01/09/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8637</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>31/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8386</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>30/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7938</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>29/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8087</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>28/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8033</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>27/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7843</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>26/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7747</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>25/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8533</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>24/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.8838</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>23/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9115</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>22/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7219</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>21/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9252</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
+          <x:t>20/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.9673</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>19/08/2026</x:t>
         </x:is>
       </x:c>
@@ -264,7 +1014,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.9041</x:v>
+        <x:v>      0.9778</x:v>
       </x:c>
     </x:row>
     <x:row>
@@ -450,6 +1200,21 @@
     <x:row>
       <x:c s="1" t="inlineStr">
         <x:is>
+          <x:t>06/08/2026</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="7" t="inlineStr">
+        <x:is>
+          <x:t>00:00</x:t>
+        </x:is>
+      </x:c>
+      <x:c s="3">
+        <x:v>      0.7122</x:v>
+      </x:c>
+    </x:row>
+    <x:row>
+      <x:c s="1" t="inlineStr">
+        <x:is>
           <x:t>05/08/2026</x:t>
         </x:is>
       </x:c>
@@ -459,7 +1224,7 @@
         </x:is>
       </x:c>
       <x:c s="3">
-        <x:v>      0.6279</x:v>
+        <x:v>      0.7568</x:v>
       </x:c>
     </x:row>
     <x:row>
